--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-AcceptDate.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-AcceptDate.xlsx
@@ -1320,7 +1320,7 @@
         <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>108</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-AcceptDate.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-EX-AcceptDate.xlsx
@@ -1320,7 +1320,7 @@
         <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>108</v>
